--- a/data/meta_analysis/analysis groups.xlsx
+++ b/data/meta_analysis/analysis groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/cat_evidence_review/data/meta_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3290F834-4755-994D-B6ED-341C61B3421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3EADC3-2F76-4E45-AA27-D80AB095E9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - determine analysis gr" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
   <si>
     <t>analysis_group_original</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Abundance with/without cats</t>
+  </si>
+  <si>
+    <t>Abundance correlation</t>
+  </si>
+  <si>
+    <t>Reproduction correlation</t>
   </si>
 </sst>
 </file>
@@ -310,7 +316,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -360,6 +366,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1571,7 +1580,9 @@
       <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
@@ -1592,7 +1603,9 @@
       <c r="F4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
@@ -1708,7 +1721,9 @@
       <c r="F9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -1730,7 +1745,9 @@
       <c r="F10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="17" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
